--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_1024_run7/epoch_60/per_file_predictions_epoch_60.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_1024_run7/epoch_60/per_file_predictions_epoch_60.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="520">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="523">
   <si>
     <t>Filename</t>
   </si>
@@ -808,772 +808,781 @@
     <t>0,1,1,0</t>
   </si>
   <si>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>1,1,0,0</t>
+  </si>
+  <si>
     <t>0,1,0,1</t>
   </si>
   <si>
-    <t>0.7801,0.2007,0.0208,0.0105</t>
-  </si>
-  <si>
-    <t>0.0098,0.0043,0.0007,0.9945</t>
-  </si>
-  <si>
-    <t>0.7668,0.0127,0.0027,0.2389</t>
-  </si>
-  <si>
-    <t>0.0434,0.0085,0.0032,0.9803</t>
-  </si>
-  <si>
-    <t>0.9972,0.0008,0.0000,0.0002</t>
-  </si>
-  <si>
-    <t>0.9960,0.0022,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.9798,0.0029,0.0006,0.0076</t>
-  </si>
-  <si>
-    <t>0.9930,0.0018,0.0010,0.0011</t>
-  </si>
-  <si>
-    <t>0.9891,0.0084,0.0008,0.0005</t>
-  </si>
-  <si>
-    <t>0.9854,0.0241,0.0006,0.0001</t>
-  </si>
-  <si>
-    <t>0.9973,0.0002,0.0000,0.0007</t>
-  </si>
-  <si>
-    <t>0.9957,0.0029,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.5999,0.0258,0.5390,0.0061</t>
-  </si>
-  <si>
-    <t>0.3637,0.2088,0.4731,0.0148</t>
-  </si>
-  <si>
-    <t>0.2527,0.0185,0.8416,0.0009</t>
-  </si>
-  <si>
-    <t>0.2846,0.0175,0.7773,0.0015</t>
-  </si>
-  <si>
-    <t>0.6930,0.0650,0.3309,0.0100</t>
-  </si>
-  <si>
-    <t>0.0505,0.9594,0.0004,0.0002</t>
-  </si>
-  <si>
-    <t>0.0334,0.9668,0.0005,0.0006</t>
-  </si>
-  <si>
-    <t>0.6674,0.4887,0.0080,0.0009</t>
-  </si>
-  <si>
-    <t>0.2865,0.8167,0.0019,0.0019</t>
-  </si>
-  <si>
-    <t>0.0133,0.9804,0.0027,0.0004</t>
-  </si>
-  <si>
-    <t>0.4634,0.0148,0.6282,0.0163</t>
-  </si>
-  <si>
-    <t>0.3087,0.0146,0.7467,0.0094</t>
-  </si>
-  <si>
-    <t>0.0367,0.0052,0.9506,0.0112</t>
-  </si>
-  <si>
-    <t>0.1733,0.2356,0.6186,0.0905</t>
-  </si>
-  <si>
-    <t>0.0667,0.0070,0.9440,0.0099</t>
-  </si>
-  <si>
-    <t>0.0044,0.0015,0.9878,0.0055</t>
-  </si>
-  <si>
-    <t>0.0021,0.0012,0.9943,0.0020</t>
-  </si>
-  <si>
-    <t>0.5245,0.6273,0.0019,0.0039</t>
-  </si>
-  <si>
-    <t>0.4255,0.4575,0.2838,0.0221</t>
-  </si>
-  <si>
-    <t>0.0057,0.0116,0.9898,0.0005</t>
-  </si>
-  <si>
-    <t>0.0201,0.9243,0.0681,0.0041</t>
-  </si>
-  <si>
-    <t>0.6877,0.2644,0.0736,0.0303</t>
-  </si>
-  <si>
-    <t>0.5090,0.2931,0.1184,0.0023</t>
-  </si>
-  <si>
-    <t>0.5996,0.5161,0.0017,0.0050</t>
-  </si>
-  <si>
-    <t>0.0272,0.9471,0.0657,0.0040</t>
-  </si>
-  <si>
-    <t>0.0392,0.7162,0.3604,0.0760</t>
-  </si>
-  <si>
-    <t>0.0223,0.2775,0.9219,0.0129</t>
-  </si>
-  <si>
-    <t>0.1039,0.0884,0.8385,0.0235</t>
-  </si>
-  <si>
-    <t>0.0877,0.0151,0.3457,0.6738</t>
-  </si>
-  <si>
-    <t>0.0181,0.0866,0.9485,0.0066</t>
-  </si>
-  <si>
-    <t>0.0129,0.9231,0.1257,0.0011</t>
-  </si>
-  <si>
-    <t>0.0182,0.1444,0.9478,0.0012</t>
-  </si>
-  <si>
-    <t>0.1906,0.5010,0.0684,0.5717</t>
-  </si>
-  <si>
-    <t>0.0061,0.9435,0.0722,0.1322</t>
-  </si>
-  <si>
-    <t>0.0094,0.9344,0.3499,0.0103</t>
-  </si>
-  <si>
-    <t>0.0012,0.9883,0.0440,0.0087</t>
-  </si>
-  <si>
-    <t>0.0192,0.2926,0.9086,0.0230</t>
-  </si>
-  <si>
-    <t>0.0060,0.0592,0.9872,0.0007</t>
-  </si>
-  <si>
-    <t>0.1291,0.0134,0.9095,0.0046</t>
-  </si>
-  <si>
-    <t>0.0097,0.0032,0.9770,0.0079</t>
-  </si>
-  <si>
-    <t>0.0059,0.0019,0.9798,0.0148</t>
-  </si>
-  <si>
-    <t>0.0031,0.0170,0.9892,0.0008</t>
-  </si>
-  <si>
-    <t>0.9645,0.0470,0.0032,0.0012</t>
-  </si>
-  <si>
-    <t>0.9799,0.0036,0.0015,0.0050</t>
-  </si>
-  <si>
-    <t>0.9848,0.0099,0.0018,0.0008</t>
-  </si>
-  <si>
-    <t>0.1050,0.0773,0.8825,0.0016</t>
-  </si>
-  <si>
-    <t>0.9824,0.0029,0.0007,0.0052</t>
-  </si>
-  <si>
-    <t>0.9780,0.0337,0.0013,0.0002</t>
-  </si>
-  <si>
-    <t>0.8144,0.3203,0.0004,0.0007</t>
-  </si>
-  <si>
-    <t>0.0097,0.7434,0.8259,0.0034</t>
-  </si>
-  <si>
-    <t>0.0063,0.0694,0.9687,0.0062</t>
-  </si>
-  <si>
-    <t>0.0267,0.0306,0.9442,0.0163</t>
-  </si>
-  <si>
-    <t>0.0005,0.4715,0.9909,0.0003</t>
-  </si>
-  <si>
-    <t>0.0064,0.0156,0.9775,0.0060</t>
-  </si>
-  <si>
-    <t>0.0233,0.9355,0.0264,0.0014</t>
-  </si>
-  <si>
-    <t>0.0084,0.9839,0.0023,0.0001</t>
-  </si>
-  <si>
-    <t>0.8557,0.0561,0.0833,0.0178</t>
-  </si>
-  <si>
-    <t>0.5887,0.1231,0.3950,0.0106</t>
-  </si>
-  <si>
-    <t>0.0489,0.0563,0.9391,0.0067</t>
-  </si>
-  <si>
-    <t>0.0011,0.8891,0.8308,0.0002</t>
-  </si>
-  <si>
-    <t>0.0031,0.8571,0.6637,0.0002</t>
-  </si>
-  <si>
-    <t>0.0007,0.9890,0.0935,0.0001</t>
-  </si>
-  <si>
-    <t>0.0022,0.9249,0.6613,0.0004</t>
-  </si>
-  <si>
-    <t>0.0202,0.0074,0.0035,0.9878</t>
-  </si>
-  <si>
-    <t>0.0036,0.0016,0.0002,0.9982</t>
-  </si>
-  <si>
-    <t>0.0056,0.0015,0.0005,0.9972</t>
-  </si>
-  <si>
-    <t>0.0203,0.0045,0.0014,0.9909</t>
-  </si>
-  <si>
-    <t>0.0887,0.0059,0.0135,0.9470</t>
-  </si>
-  <si>
-    <t>0.0047,0.0056,0.0316,0.9894</t>
-  </si>
-  <si>
-    <t>0.0001,0.9778,0.9173,0.0000</t>
-  </si>
-  <si>
-    <t>0.0023,0.5139,0.9660,0.0005</t>
-  </si>
-  <si>
-    <t>0.0392,0.6182,0.5081,0.0085</t>
-  </si>
-  <si>
-    <t>0.0575,0.0952,0.9353,0.0015</t>
-  </si>
-  <si>
-    <t>0.0005,0.9455,0.5448,0.0000</t>
-  </si>
-  <si>
-    <t>0.0076,0.8815,0.5560,0.0017</t>
-  </si>
-  <si>
-    <t>0.9842,0.0094,0.0009,0.0015</t>
-  </si>
-  <si>
-    <t>0.9437,0.0770,0.0006,0.0011</t>
-  </si>
-  <si>
-    <t>0.9942,0.0083,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.9881,0.0033,0.0003,0.0019</t>
-  </si>
-  <si>
-    <t>0.9845,0.0168,0.0006,0.0005</t>
-  </si>
-  <si>
-    <t>0.9909,0.0053,0.0005,0.0007</t>
-  </si>
-  <si>
-    <t>0.9783,0.0349,0.0005,0.0003</t>
-  </si>
-  <si>
-    <t>0.9809,0.0143,0.0076,0.0006</t>
-  </si>
-  <si>
-    <t>0.9952,0.0015,0.0001,0.0006</t>
-  </si>
-  <si>
-    <t>0.9965,0.0020,0.0009,0.0001</t>
-  </si>
-  <si>
-    <t>0.9964,0.0005,0.0000,0.0007</t>
-  </si>
-  <si>
-    <t>0.9959,0.0016,0.0002,0.0003</t>
-  </si>
-  <si>
-    <t>0.9967,0.0013,0.0003,0.0002</t>
-  </si>
-  <si>
-    <t>0.9977,0.0012,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9970,0.0008,0.0001,0.0003</t>
-  </si>
-  <si>
-    <t>0.9938,0.0014,0.0001,0.0009</t>
-  </si>
-  <si>
-    <t>0.0150,0.0014,0.9835,0.0022</t>
-  </si>
-  <si>
-    <t>0.1229,0.0555,0.8300,0.0356</t>
-  </si>
-  <si>
-    <t>0.6542,0.0275,0.2619,0.0658</t>
-  </si>
-  <si>
-    <t>0.0336,0.0163,0.9499,0.0064</t>
-  </si>
-  <si>
-    <t>0.0507,0.9333,0.0048,0.0055</t>
-  </si>
-  <si>
-    <t>0.0159,0.9780,0.0033,0.0008</t>
-  </si>
-  <si>
-    <t>0.0987,0.9002,0.0048,0.0054</t>
-  </si>
-  <si>
-    <t>0.3698,0.7410,0.0012,0.0019</t>
-  </si>
-  <si>
-    <t>0.0566,0.9256,0.0007,0.0078</t>
-  </si>
-  <si>
-    <t>0.0139,0.9788,0.0017,0.0005</t>
-  </si>
-  <si>
-    <t>0.7885,0.3149,0.0060,0.0011</t>
-  </si>
-  <si>
-    <t>0.6594,0.0994,0.3067,0.0326</t>
-  </si>
-  <si>
-    <t>0.2875,0.0149,0.7884,0.0156</t>
-  </si>
-  <si>
-    <t>0.2100,0.5925,0.0411,0.1518</t>
-  </si>
-  <si>
-    <t>0.2604,0.2283,0.5069,0.0069</t>
-  </si>
-  <si>
-    <t>0.0179,0.6242,0.0275,0.8909</t>
-  </si>
-  <si>
-    <t>0.0029,0.9845,0.0223,0.0089</t>
-  </si>
-  <si>
-    <t>0.0019,0.9875,0.0162,0.0084</t>
-  </si>
-  <si>
-    <t>0.0080,0.9588,0.0122,0.1151</t>
-  </si>
-  <si>
-    <t>0.0001,0.9833,0.8720,0.0001</t>
-  </si>
-  <si>
-    <t>0.0138,0.9519,0.1875,0.0033</t>
-  </si>
-  <si>
-    <t>0.7127,0.4743,0.0026,0.0011</t>
-  </si>
-  <si>
-    <t>0.6054,0.5145,0.0047,0.0032</t>
-  </si>
-  <si>
-    <t>0.9884,0.0065,0.0004,0.0013</t>
-  </si>
-  <si>
-    <t>0.9726,0.0398,0.0012,0.0004</t>
-  </si>
-  <si>
-    <t>0.9720,0.0116,0.0048,0.0039</t>
-  </si>
-  <si>
-    <t>0.9831,0.0083,0.0023,0.0012</t>
-  </si>
-  <si>
-    <t>0.9918,0.0064,0.0024,0.0002</t>
-  </si>
-  <si>
-    <t>0.9786,0.0241,0.0015,0.0008</t>
-  </si>
-  <si>
-    <t>0.9757,0.0080,0.0028,0.0041</t>
-  </si>
-  <si>
-    <t>0.9761,0.0075,0.0017,0.0043</t>
-  </si>
-  <si>
-    <t>0.0016,0.8838,0.8723,0.0004</t>
-  </si>
-  <si>
-    <t>0.0027,0.8233,0.7580,0.0004</t>
-  </si>
-  <si>
-    <t>0.0222,0.3547,0.8405,0.0063</t>
-  </si>
-  <si>
-    <t>0.0810,0.2764,0.6473,0.0031</t>
-  </si>
-  <si>
-    <t>0.7497,0.0472,0.1535,0.0432</t>
-  </si>
-  <si>
-    <t>0.3126,0.2812,0.4554,0.0390</t>
-  </si>
-  <si>
-    <t>0.0936,0.0037,0.9587,0.0006</t>
-  </si>
-  <si>
-    <t>0.4195,0.2914,0.2312,0.1338</t>
-  </si>
-  <si>
-    <t>0.4663,0.0098,0.0028,0.7164</t>
-  </si>
-  <si>
-    <t>0.0004,0.0064,0.0034,0.9986</t>
-  </si>
-  <si>
-    <t>0.0083,0.0061,0.0031,0.9933</t>
-  </si>
-  <si>
-    <t>0.0022,0.0102,0.0014,0.9971</t>
-  </si>
-  <si>
-    <t>0.0008,0.8512,0.9532,0.0003</t>
-  </si>
-  <si>
-    <t>0.9692,0.0212,0.0012,0.0032</t>
-  </si>
-  <si>
-    <t>0.7723,0.2951,0.0176,0.0047</t>
-  </si>
-  <si>
-    <t>0.9696,0.0303,0.0027,0.0016</t>
-  </si>
-  <si>
-    <t>0.8558,0.2387,0.0020,0.0013</t>
-  </si>
-  <si>
-    <t>0.9273,0.0430,0.0221,0.0066</t>
-  </si>
-  <si>
-    <t>0.7832,0.0032,0.0013,0.2973</t>
-  </si>
-  <si>
-    <t>0.9733,0.0176,0.0015,0.0024</t>
-  </si>
-  <si>
-    <t>0.0021,0.1196,0.9490,0.0727</t>
-  </si>
-  <si>
-    <t>0.6303,0.0008,0.0034,0.5393</t>
-  </si>
-  <si>
-    <t>0.4467,0.0354,0.0410,0.6169</t>
-  </si>
-  <si>
-    <t>0.6721,0.3094,0.0028,0.0176</t>
-  </si>
-  <si>
-    <t>0.9210,0.0348,0.0129,0.0062</t>
-  </si>
-  <si>
-    <t>0.9097,0.0457,0.0276,0.0093</t>
-  </si>
-  <si>
-    <t>0.0957,0.8266,0.0414,0.0618</t>
-  </si>
-  <si>
-    <t>0.8871,0.0776,0.0329,0.0021</t>
-  </si>
-  <si>
-    <t>0.8980,0.0584,0.0216,0.0076</t>
-  </si>
-  <si>
-    <t>0.9932,0.0015,0.0004,0.0010</t>
-  </si>
-  <si>
-    <t>0.9787,0.0107,0.0015,0.0032</t>
-  </si>
-  <si>
-    <t>0.9880,0.0022,0.0005,0.0033</t>
-  </si>
-  <si>
-    <t>0.9852,0.0016,0.0002,0.0056</t>
-  </si>
-  <si>
-    <t>0.9789,0.0127,0.0022,0.0018</t>
-  </si>
-  <si>
-    <t>0.9758,0.0212,0.0012,0.0013</t>
-  </si>
-  <si>
-    <t>0.9725,0.0094,0.0028,0.0050</t>
-  </si>
-  <si>
-    <t>0.9881,0.0004,0.0000,0.0076</t>
-  </si>
-  <si>
-    <t>0.4998,0.5388,0.0159,0.0268</t>
-  </si>
-  <si>
-    <t>0.4072,0.7252,0.0061,0.0015</t>
-  </si>
-  <si>
-    <t>0.6894,0.4731,0.0011,0.0012</t>
-  </si>
-  <si>
-    <t>0.7509,0.1536,0.1449,0.0176</t>
-  </si>
-  <si>
-    <t>0.9171,0.0995,0.0029,0.0027</t>
-  </si>
-  <si>
-    <t>0.9294,0.0285,0.0210,0.0097</t>
-  </si>
-  <si>
-    <t>0.9548,0.0707,0.0026,0.0006</t>
-  </si>
-  <si>
-    <t>0.6810,0.4023,0.0119,0.0046</t>
-  </si>
-  <si>
-    <t>0.0010,0.0241,0.9960,0.0001</t>
-  </si>
-  <si>
-    <t>0.9595,0.0349,0.0046,0.0020</t>
-  </si>
-  <si>
-    <t>0.0033,0.0243,0.9896,0.0007</t>
-  </si>
-  <si>
-    <t>0.0025,0.0494,0.9852,0.0044</t>
-  </si>
-  <si>
-    <t>0.0268,0.0127,0.9443,0.0234</t>
-  </si>
-  <si>
-    <t>0.0031,0.5509,0.9713,0.0011</t>
-  </si>
-  <si>
-    <t>0.0423,0.0265,0.9524,0.0021</t>
-  </si>
-  <si>
-    <t>0.0043,0.0027,0.9958,0.0003</t>
-  </si>
-  <si>
-    <t>0.0114,0.0205,0.9777,0.0039</t>
-  </si>
-  <si>
-    <t>0.1213,0.4534,0.4048,0.0246</t>
-  </si>
-  <si>
-    <t>0.4071,0.0051,0.6616,0.0254</t>
-  </si>
-  <si>
-    <t>0.5981,0.0407,0.4909,0.0092</t>
-  </si>
-  <si>
-    <t>0.3739,0.1618,0.5488,0.0169</t>
-  </si>
-  <si>
-    <t>0.0453,0.6221,0.4240,0.0105</t>
-  </si>
-  <si>
-    <t>0.5272,0.2084,0.2901,0.0084</t>
-  </si>
-  <si>
-    <t>0.0610,0.8309,0.1031,0.0854</t>
-  </si>
-  <si>
-    <t>0.3879,0.0323,0.6570,0.0025</t>
-  </si>
-  <si>
-    <t>0.7876,0.2894,0.0045,0.0052</t>
-  </si>
-  <si>
-    <t>0.8734,0.3363,0.0005,0.0001</t>
-  </si>
-  <si>
-    <t>0.9068,0.1429,0.0055,0.0016</t>
-  </si>
-  <si>
-    <t>0.8610,0.2518,0.0015,0.0010</t>
-  </si>
-  <si>
-    <t>0.9040,0.1041,0.0011,0.0030</t>
-  </si>
-  <si>
-    <t>0.2326,0.5319,0.2794,0.1580</t>
-  </si>
-  <si>
-    <t>0.8262,0.0151,0.0493,0.0457</t>
-  </si>
-  <si>
-    <t>0.1418,0.0399,0.0296,0.8967</t>
-  </si>
-  <si>
-    <t>0.5064,0.1195,0.4006,0.0109</t>
-  </si>
-  <si>
-    <t>0.7672,0.0581,0.1572,0.0124</t>
-  </si>
-  <si>
-    <t>0.0805,0.1972,0.6938,0.0200</t>
-  </si>
-  <si>
-    <t>0.2241,0.1995,0.5867,0.1568</t>
-  </si>
-  <si>
-    <t>0.0157,0.5261,0.8879,0.0101</t>
-  </si>
-  <si>
-    <t>0.0418,0.1140,0.9171,0.0035</t>
-  </si>
-  <si>
-    <t>0.0240,0.1721,0.8977,0.0061</t>
-  </si>
-  <si>
-    <t>0.9918,0.0007,0.0000,0.0035</t>
-  </si>
-  <si>
-    <t>0.9684,0.0289,0.0053,0.0012</t>
-  </si>
-  <si>
-    <t>0.9749,0.0310,0.0041,0.0007</t>
-  </si>
-  <si>
-    <t>0.9886,0.0104,0.0008,0.0004</t>
-  </si>
-  <si>
-    <t>0.9781,0.0426,0.0006,0.0002</t>
-  </si>
-  <si>
-    <t>0.9910,0.0070,0.0003,0.0004</t>
-  </si>
-  <si>
-    <t>0.9807,0.0064,0.0002,0.0031</t>
-  </si>
-  <si>
-    <t>0.9825,0.0154,0.0035,0.0007</t>
-  </si>
-  <si>
-    <t>0.2955,0.0140,0.8155,0.0075</t>
-  </si>
-  <si>
-    <t>0.1690,0.4441,0.5031,0.0178</t>
-  </si>
-  <si>
-    <t>0.7329,0.0243,0.2772,0.0170</t>
-  </si>
-  <si>
-    <t>0.0120,0.0090,0.9799,0.0035</t>
-  </si>
-  <si>
-    <t>0.0059,0.0121,0.9885,0.0010</t>
-  </si>
-  <si>
-    <t>0.0128,0.0410,0.9783,0.0007</t>
-  </si>
-  <si>
-    <t>0.0053,0.0095,0.9909,0.0007</t>
-  </si>
-  <si>
-    <t>0.0676,0.0690,0.8770,0.0016</t>
-  </si>
-  <si>
-    <t>0.0112,0.0056,0.9874,0.0007</t>
-  </si>
-  <si>
-    <t>0.0459,0.0591,0.9221,0.0150</t>
-  </si>
-  <si>
-    <t>0.0631,0.5496,0.5170,0.0559</t>
-  </si>
-  <si>
-    <t>0.5356,0.0223,0.5594,0.0147</t>
-  </si>
-  <si>
-    <t>0.5889,0.0043,0.3520,0.0713</t>
-  </si>
-  <si>
-    <t>0.7721,0.0141,0.2156,0.0234</t>
-  </si>
-  <si>
-    <t>0.9642,0.0762,0.0014,0.0001</t>
-  </si>
-  <si>
-    <t>0.9907,0.0079,0.0008,0.0004</t>
-  </si>
-  <si>
-    <t>0.9907,0.0076,0.0002,0.0004</t>
-  </si>
-  <si>
-    <t>0.9806,0.0225,0.0020,0.0005</t>
-  </si>
-  <si>
-    <t>0.9680,0.0328,0.0035,0.0015</t>
-  </si>
-  <si>
-    <t>0.9557,0.0650,0.0007,0.0008</t>
-  </si>
-  <si>
-    <t>0.9902,0.0235,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9871,0.0213,0.0004,0.0002</t>
-  </si>
-  <si>
-    <t>0.0211,0.0720,0.9282,0.0103</t>
-  </si>
-  <si>
-    <t>0.0100,0.2134,0.9422,0.0084</t>
-  </si>
-  <si>
-    <t>0.0137,0.0335,0.9762,0.0018</t>
-  </si>
-  <si>
-    <t>0.1452,0.0644,0.7539,0.0125</t>
-  </si>
-  <si>
-    <t>0.0169,0.0039,0.9896,0.0003</t>
-  </si>
-  <si>
-    <t>0.2680,0.0547,0.5539,0.2092</t>
-  </si>
-  <si>
-    <t>0.0081,0.0201,0.9629,0.0289</t>
-  </si>
-  <si>
-    <t>0.0256,0.0633,0.8405,0.1360</t>
-  </si>
-  <si>
-    <t>0.4317,0.0009,0.0014,0.8054</t>
-  </si>
-  <si>
-    <t>0.0047,0.0528,0.0088,0.9902</t>
-  </si>
-  <si>
-    <t>0.0218,0.0003,0.0001,0.9951</t>
-  </si>
-  <si>
-    <t>0.0099,0.0008,0.0044,0.9927</t>
-  </si>
-  <si>
-    <t>0.0028,0.0002,0.0002,0.9986</t>
-  </si>
-  <si>
-    <t>0.6939,0.0702,0.0306,0.2112</t>
+    <t>1,0,0,1</t>
+  </si>
+  <si>
+    <t>0.8706,0.0108,0.0488,0.0267</t>
+  </si>
+  <si>
+    <t>0.0231,0.0158,0.0050,0.9837</t>
+  </si>
+  <si>
+    <t>0.1809,0.1836,0.0044,0.7078</t>
+  </si>
+  <si>
+    <t>0.1593,0.0028,0.0080,0.9274</t>
+  </si>
+  <si>
+    <t>0.9979,0.0003,0.0000,0.0004</t>
+  </si>
+  <si>
+    <t>0.9949,0.0017,0.0001,0.0005</t>
+  </si>
+  <si>
+    <t>0.9819,0.0095,0.0034,0.0018</t>
+  </si>
+  <si>
+    <t>0.9901,0.0009,0.0004,0.0039</t>
+  </si>
+  <si>
+    <t>0.9926,0.0043,0.0001,0.0005</t>
+  </si>
+  <si>
+    <t>0.9946,0.0053,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.9932,0.0061,0.0005,0.0002</t>
+  </si>
+  <si>
+    <t>0.9907,0.0008,0.0001,0.0034</t>
+  </si>
+  <si>
+    <t>0.3518,0.3524,0.3876,0.0752</t>
+  </si>
+  <si>
+    <t>0.2386,0.1256,0.6649,0.0098</t>
+  </si>
+  <si>
+    <t>0.2345,0.0813,0.7117,0.0031</t>
+  </si>
+  <si>
+    <t>0.1416,0.0352,0.8264,0.0016</t>
+  </si>
+  <si>
+    <t>0.8152,0.0634,0.1141,0.0063</t>
+  </si>
+  <si>
+    <t>0.0046,0.9910,0.0003,0.0006</t>
+  </si>
+  <si>
+    <t>0.0333,0.9637,0.0004,0.0013</t>
+  </si>
+  <si>
+    <t>0.6908,0.3774,0.0098,0.0091</t>
+  </si>
+  <si>
+    <t>0.5554,0.5667,0.0022,0.0045</t>
+  </si>
+  <si>
+    <t>0.0635,0.9395,0.0014,0.0006</t>
+  </si>
+  <si>
+    <t>0.5355,0.0151,0.4333,0.0561</t>
+  </si>
+  <si>
+    <t>0.1904,0.0657,0.6802,0.1063</t>
+  </si>
+  <si>
+    <t>0.0648,0.0444,0.9368,0.0061</t>
+  </si>
+  <si>
+    <t>0.2083,0.0180,0.8454,0.0063</t>
+  </si>
+  <si>
+    <t>0.3255,0.0555,0.6772,0.0168</t>
+  </si>
+  <si>
+    <t>0.0622,0.1052,0.8162,0.0109</t>
+  </si>
+  <si>
+    <t>0.0003,0.0004,0.9982,0.0010</t>
+  </si>
+  <si>
+    <t>0.6574,0.5568,0.0021,0.0008</t>
+  </si>
+  <si>
+    <t>0.5713,0.1244,0.4211,0.0225</t>
+  </si>
+  <si>
+    <t>0.0052,0.0046,0.9867,0.0052</t>
+  </si>
+  <si>
+    <t>0.0302,0.8987,0.1059,0.0051</t>
+  </si>
+  <si>
+    <t>0.7988,0.1549,0.0242,0.0200</t>
+  </si>
+  <si>
+    <t>0.4054,0.5795,0.0420,0.0074</t>
+  </si>
+  <si>
+    <t>0.7603,0.3929,0.0027,0.0021</t>
+  </si>
+  <si>
+    <t>0.0294,0.9502,0.0844,0.0083</t>
+  </si>
+  <si>
+    <t>0.0129,0.9134,0.0731,0.0139</t>
+  </si>
+  <si>
+    <t>0.3481,0.0513,0.6478,0.0483</t>
+  </si>
+  <si>
+    <t>0.0558,0.1451,0.8413,0.0311</t>
+  </si>
+  <si>
+    <t>0.1402,0.0388,0.8565,0.0076</t>
+  </si>
+  <si>
+    <t>0.0125,0.1493,0.9339,0.0006</t>
+  </si>
+  <si>
+    <t>0.0153,0.9487,0.0272,0.0007</t>
+  </si>
+  <si>
+    <t>0.0219,0.2622,0.8686,0.0199</t>
+  </si>
+  <si>
+    <t>0.0070,0.8661,0.0051,0.6709</t>
+  </si>
+  <si>
+    <t>0.0082,0.9561,0.0228,0.0627</t>
+  </si>
+  <si>
+    <t>0.0036,0.9794,0.0462,0.0030</t>
+  </si>
+  <si>
+    <t>0.0050,0.9794,0.0401,0.0038</t>
+  </si>
+  <si>
+    <t>0.0495,0.0766,0.9104,0.0135</t>
+  </si>
+  <si>
+    <t>0.0018,0.1269,0.9900,0.0005</t>
+  </si>
+  <si>
+    <t>0.0562,0.0094,0.9462,0.0043</t>
+  </si>
+  <si>
+    <t>0.0349,0.0049,0.9773,0.0013</t>
+  </si>
+  <si>
+    <t>0.0198,0.0218,0.9722,0.0025</t>
+  </si>
+  <si>
+    <t>0.0013,0.0066,0.9961,0.0001</t>
+  </si>
+  <si>
+    <t>0.9530,0.0659,0.0006,0.0008</t>
+  </si>
+  <si>
+    <t>0.9785,0.0168,0.0026,0.0011</t>
+  </si>
+  <si>
+    <t>0.9704,0.0220,0.0012,0.0022</t>
+  </si>
+  <si>
+    <t>0.0043,0.0103,0.9870,0.0038</t>
+  </si>
+  <si>
+    <t>0.9838,0.0143,0.0030,0.0004</t>
+  </si>
+  <si>
+    <t>0.9934,0.0027,0.0003,0.0006</t>
+  </si>
+  <si>
+    <t>0.9607,0.0544,0.0008,0.0010</t>
+  </si>
+  <si>
+    <t>0.0080,0.2608,0.9603,0.0029</t>
+  </si>
+  <si>
+    <t>0.0065,0.0971,0.9738,0.0044</t>
+  </si>
+  <si>
+    <t>0.0052,0.2577,0.8852,0.0302</t>
+  </si>
+  <si>
+    <t>0.0003,0.9076,0.9766,0.0001</t>
+  </si>
+  <si>
+    <t>0.0114,0.0035,0.9875,0.0010</t>
+  </si>
+  <si>
+    <t>0.1329,0.7544,0.0690,0.0019</t>
+  </si>
+  <si>
+    <t>0.0061,0.9853,0.0029,0.0008</t>
+  </si>
+  <si>
+    <t>0.9403,0.0317,0.0127,0.0039</t>
+  </si>
+  <si>
+    <t>0.8355,0.0767,0.0905,0.0114</t>
+  </si>
+  <si>
+    <t>0.0304,0.0539,0.9419,0.0004</t>
+  </si>
+  <si>
+    <t>0.0011,0.9378,0.8949,0.0003</t>
+  </si>
+  <si>
+    <t>0.0020,0.6700,0.8196,0.0001</t>
+  </si>
+  <si>
+    <t>0.0028,0.9663,0.1577,0.0004</t>
+  </si>
+  <si>
+    <t>0.0019,0.9305,0.5698,0.0003</t>
+  </si>
+  <si>
+    <t>0.1544,0.0077,0.0378,0.8648</t>
+  </si>
+  <si>
+    <t>0.0048,0.0035,0.0006,0.9972</t>
+  </si>
+  <si>
+    <t>0.0049,0.0053,0.0023,0.9960</t>
+  </si>
+  <si>
+    <t>0.0204,0.0103,0.0059,0.9861</t>
+  </si>
+  <si>
+    <t>0.0036,0.0087,0.0060,0.9952</t>
+  </si>
+  <si>
+    <t>0.0060,0.0002,0.0001,0.9984</t>
+  </si>
+  <si>
+    <t>0.0014,0.9427,0.7563,0.0002</t>
+  </si>
+  <si>
+    <t>0.0035,0.5241,0.9638,0.0020</t>
+  </si>
+  <si>
+    <t>0.0170,0.5691,0.7919,0.0038</t>
+  </si>
+  <si>
+    <t>0.0072,0.4630,0.9342,0.0017</t>
+  </si>
+  <si>
+    <t>0.0022,0.9459,0.5218,0.0004</t>
+  </si>
+  <si>
+    <t>0.0007,0.9720,0.5912,0.0001</t>
+  </si>
+  <si>
+    <t>0.9869,0.0136,0.0015,0.0005</t>
+  </si>
+  <si>
+    <t>0.9902,0.0088,0.0009,0.0004</t>
+  </si>
+  <si>
+    <t>0.9868,0.0114,0.0007,0.0005</t>
+  </si>
+  <si>
+    <t>0.9903,0.0131,0.0004,0.0002</t>
+  </si>
+  <si>
+    <t>0.9766,0.0223,0.0035,0.0010</t>
+  </si>
+  <si>
+    <t>0.9935,0.0008,0.0000,0.0012</t>
+  </si>
+  <si>
+    <t>0.9877,0.0142,0.0002,0.0003</t>
+  </si>
+  <si>
+    <t>0.9919,0.0113,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.9963,0.0014,0.0005,0.0002</t>
+  </si>
+  <si>
+    <t>0.9939,0.0049,0.0006,0.0003</t>
+  </si>
+  <si>
+    <t>0.9965,0.0002,0.0000,0.0012</t>
+  </si>
+  <si>
+    <t>0.9951,0.0010,0.0001,0.0009</t>
+  </si>
+  <si>
+    <t>0.9964,0.0006,0.0000,0.0005</t>
+  </si>
+  <si>
+    <t>0.9968,0.0012,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9953,0.0007,0.0001,0.0011</t>
+  </si>
+  <si>
+    <t>0.9913,0.0052,0.0004,0.0005</t>
+  </si>
+  <si>
+    <t>0.0165,0.0036,0.9775,0.0055</t>
+  </si>
+  <si>
+    <t>0.0771,0.0172,0.9285,0.0034</t>
+  </si>
+  <si>
+    <t>0.5525,0.0707,0.3327,0.0723</t>
+  </si>
+  <si>
+    <t>0.0259,0.0739,0.9247,0.0021</t>
+  </si>
+  <si>
+    <t>0.1678,0.8411,0.0064,0.0113</t>
+  </si>
+  <si>
+    <t>0.0377,0.9583,0.0076,0.0021</t>
+  </si>
+  <si>
+    <t>0.0417,0.9432,0.0016,0.0071</t>
+  </si>
+  <si>
+    <t>0.2914,0.7525,0.0003,0.0024</t>
+  </si>
+  <si>
+    <t>0.1487,0.8715,0.0020,0.0048</t>
+  </si>
+  <si>
+    <t>0.0249,0.9666,0.0044,0.0013</t>
+  </si>
+  <si>
+    <t>0.5489,0.6432,0.0008,0.0007</t>
+  </si>
+  <si>
+    <t>0.6109,0.0342,0.4543,0.0275</t>
+  </si>
+  <si>
+    <t>0.2647,0.0146,0.7862,0.0269</t>
+  </si>
+  <si>
+    <t>0.6538,0.1475,0.1888,0.0201</t>
+  </si>
+  <si>
+    <t>0.5049,0.0462,0.4617,0.0903</t>
+  </si>
+  <si>
+    <t>0.1696,0.2076,0.0297,0.8013</t>
+  </si>
+  <si>
+    <t>0.0048,0.9780,0.0236,0.0197</t>
+  </si>
+  <si>
+    <t>0.0014,0.9863,0.0344,0.0123</t>
+  </si>
+  <si>
+    <t>0.0011,0.9910,0.0015,0.0172</t>
+  </si>
+  <si>
+    <t>0.0002,0.9769,0.7283,0.0003</t>
+  </si>
+  <si>
+    <t>0.0070,0.9857,0.0284,0.0007</t>
+  </si>
+  <si>
+    <t>0.7906,0.3027,0.0040,0.0029</t>
+  </si>
+  <si>
+    <t>0.1783,0.8276,0.0073,0.0069</t>
+  </si>
+  <si>
+    <t>0.9872,0.0055,0.0022,0.0012</t>
+  </si>
+  <si>
+    <t>0.9872,0.0069,0.0008,0.0011</t>
+  </si>
+  <si>
+    <t>0.9827,0.0024,0.0019,0.0051</t>
+  </si>
+  <si>
+    <t>0.9761,0.0054,0.0023,0.0053</t>
+  </si>
+  <si>
+    <t>0.9928,0.0030,0.0006,0.0006</t>
+  </si>
+  <si>
+    <t>0.9848,0.0089,0.0022,0.0009</t>
+  </si>
+  <si>
+    <t>0.9774,0.0103,0.0035,0.0028</t>
+  </si>
+  <si>
+    <t>0.9599,0.0519,0.0030,0.0007</t>
+  </si>
+  <si>
+    <t>0.0012,0.7956,0.8916,0.0002</t>
+  </si>
+  <si>
+    <t>0.0036,0.7687,0.8475,0.0004</t>
+  </si>
+  <si>
+    <t>0.0071,0.6910,0.8519,0.0030</t>
+  </si>
+  <si>
+    <t>0.0626,0.2939,0.7783,0.0203</t>
+  </si>
+  <si>
+    <t>0.8502,0.0168,0.0219,0.0687</t>
+  </si>
+  <si>
+    <t>0.5593,0.1267,0.4059,0.0333</t>
+  </si>
+  <si>
+    <t>0.4652,0.0071,0.7579,0.0004</t>
+  </si>
+  <si>
+    <t>0.6523,0.1701,0.1956,0.0274</t>
+  </si>
+  <si>
+    <t>0.0283,0.0023,0.0119,0.9788</t>
+  </si>
+  <si>
+    <t>0.0005,0.0022,0.0022,0.9990</t>
+  </si>
+  <si>
+    <t>0.0025,0.0005,0.0026,0.9971</t>
+  </si>
+  <si>
+    <t>0.0038,0.0129,0.0006,0.9963</t>
+  </si>
+  <si>
+    <t>0.0064,0.9442,0.1736,0.0001</t>
+  </si>
+  <si>
+    <t>0.9760,0.0094,0.0006,0.0038</t>
+  </si>
+  <si>
+    <t>0.4204,0.6746,0.0047,0.0045</t>
+  </si>
+  <si>
+    <t>0.9690,0.0131,0.0010,0.0049</t>
+  </si>
+  <si>
+    <t>0.7335,0.4169,0.0048,0.0007</t>
+  </si>
+  <si>
+    <t>0.9514,0.0141,0.0104,0.0078</t>
+  </si>
+  <si>
+    <t>0.5315,0.0046,0.0055,0.6315</t>
+  </si>
+  <si>
+    <t>0.9461,0.0393,0.0068,0.0047</t>
+  </si>
+  <si>
+    <t>0.0005,0.1414,0.9598,0.0501</t>
+  </si>
+  <si>
+    <t>0.9131,0.0018,0.0116,0.0378</t>
+  </si>
+  <si>
+    <t>0.8900,0.0293,0.0152,0.0313</t>
+  </si>
+  <si>
+    <t>0.7573,0.2955,0.0050,0.0053</t>
+  </si>
+  <si>
+    <t>0.8965,0.0975,0.0034,0.0082</t>
+  </si>
+  <si>
+    <t>0.7077,0.3177,0.0438,0.0237</t>
+  </si>
+  <si>
+    <t>0.2623,0.6741,0.0453,0.0321</t>
+  </si>
+  <si>
+    <t>0.8900,0.1032,0.0126,0.0058</t>
+  </si>
+  <si>
+    <t>0.8747,0.0942,0.0130,0.0122</t>
+  </si>
+  <si>
+    <t>0.9927,0.0001,0.0000,0.0063</t>
+  </si>
+  <si>
+    <t>0.9741,0.0168,0.0044,0.0030</t>
+  </si>
+  <si>
+    <t>0.9866,0.0034,0.0014,0.0032</t>
+  </si>
+  <si>
+    <t>0.9908,0.0006,0.0002,0.0044</t>
+  </si>
+  <si>
+    <t>0.9676,0.0299,0.0063,0.0012</t>
+  </si>
+  <si>
+    <t>0.9794,0.0176,0.0012,0.0011</t>
+  </si>
+  <si>
+    <t>0.9914,0.0031,0.0003,0.0010</t>
+  </si>
+  <si>
+    <t>0.9881,0.0017,0.0008,0.0032</t>
+  </si>
+  <si>
+    <t>0.6172,0.4570,0.0056,0.0097</t>
+  </si>
+  <si>
+    <t>0.5132,0.6568,0.0010,0.0010</t>
+  </si>
+  <si>
+    <t>0.6475,0.4842,0.0043,0.0019</t>
+  </si>
+  <si>
+    <t>0.4253,0.5038,0.1720,0.0203</t>
+  </si>
+  <si>
+    <t>0.9485,0.0598,0.0037,0.0010</t>
+  </si>
+  <si>
+    <t>0.8337,0.1164,0.0654,0.0099</t>
+  </si>
+  <si>
+    <t>0.9745,0.0353,0.0010,0.0004</t>
+  </si>
+  <si>
+    <t>0.8053,0.1670,0.0008,0.0078</t>
+  </si>
+  <si>
+    <t>0.0070,0.0249,0.9905,0.0003</t>
+  </si>
+  <si>
+    <t>0.9699,0.0216,0.0014,0.0024</t>
+  </si>
+  <si>
+    <t>0.0017,0.0062,0.9940,0.0012</t>
+  </si>
+  <si>
+    <t>0.0029,0.4670,0.9610,0.0031</t>
+  </si>
+  <si>
+    <t>0.1555,0.0370,0.8336,0.0080</t>
+  </si>
+  <si>
+    <t>0.0092,0.0984,0.9738,0.0020</t>
+  </si>
+  <si>
+    <t>0.0086,0.1870,0.9614,0.0014</t>
+  </si>
+  <si>
+    <t>0.0272,0.0045,0.9739,0.0029</t>
+  </si>
+  <si>
+    <t>0.0026,0.0014,0.9951,0.0008</t>
+  </si>
+  <si>
+    <t>0.4158,0.0229,0.6818,0.0107</t>
+  </si>
+  <si>
+    <t>0.1394,0.1294,0.7669,0.0125</t>
+  </si>
+  <si>
+    <t>0.0939,0.0865,0.8723,0.0032</t>
+  </si>
+  <si>
+    <t>0.3257,0.1164,0.5932,0.0025</t>
+  </si>
+  <si>
+    <t>0.1297,0.7196,0.1295,0.0875</t>
+  </si>
+  <si>
+    <t>0.1853,0.6472,0.1467,0.0333</t>
+  </si>
+  <si>
+    <t>0.1955,0.0853,0.5743,0.3570</t>
+  </si>
+  <si>
+    <t>0.4606,0.0400,0.5982,0.0347</t>
+  </si>
+  <si>
+    <t>0.9359,0.0788,0.0042,0.0013</t>
+  </si>
+  <si>
+    <t>0.8937,0.1701,0.0015,0.0012</t>
+  </si>
+  <si>
+    <t>0.8767,0.1834,0.0025,0.0025</t>
+  </si>
+  <si>
+    <t>0.8934,0.1824,0.0059,0.0006</t>
+  </si>
+  <si>
+    <t>0.6454,0.5422,0.0014,0.0005</t>
+  </si>
+  <si>
+    <t>0.6334,0.1510,0.2013,0.0596</t>
+  </si>
+  <si>
+    <t>0.7824,0.0330,0.2118,0.0099</t>
+  </si>
+  <si>
+    <t>0.4428,0.2910,0.1201,0.1396</t>
+  </si>
+  <si>
+    <t>0.6559,0.0180,0.4406,0.0148</t>
+  </si>
+  <si>
+    <t>0.7619,0.0236,0.1659,0.0397</t>
+  </si>
+  <si>
+    <t>0.0329,0.0556,0.9349,0.0179</t>
+  </si>
+  <si>
+    <t>0.0350,0.1279,0.8791,0.0398</t>
+  </si>
+  <si>
+    <t>0.0181,0.3308,0.9082,0.0086</t>
+  </si>
+  <si>
+    <t>0.1684,0.1526,0.7324,0.0140</t>
+  </si>
+  <si>
+    <t>0.0029,0.0859,0.9698,0.0050</t>
+  </si>
+  <si>
+    <t>0.9820,0.0077,0.0002,0.0021</t>
+  </si>
+  <si>
+    <t>0.9892,0.0096,0.0004,0.0005</t>
+  </si>
+  <si>
+    <t>0.9763,0.0170,0.0002,0.0012</t>
+  </si>
+  <si>
+    <t>0.9806,0.0190,0.0022,0.0008</t>
+  </si>
+  <si>
+    <t>0.9905,0.0079,0.0008,0.0004</t>
+  </si>
+  <si>
+    <t>0.9933,0.0024,0.0001,0.0007</t>
+  </si>
+  <si>
+    <t>0.9922,0.0037,0.0001,0.0006</t>
+  </si>
+  <si>
+    <t>0.9924,0.0039,0.0007,0.0004</t>
+  </si>
+  <si>
+    <t>0.0347,0.0113,0.9694,0.0027</t>
+  </si>
+  <si>
+    <t>0.6083,0.1045,0.3936,0.0022</t>
+  </si>
+  <si>
+    <t>0.9153,0.0274,0.0719,0.0033</t>
+  </si>
+  <si>
+    <t>0.0328,0.0274,0.9470,0.0042</t>
+  </si>
+  <si>
+    <t>0.0038,0.0150,0.9789,0.0104</t>
+  </si>
+  <si>
+    <t>0.0285,0.0218,0.9725,0.0011</t>
+  </si>
+  <si>
+    <t>0.0050,0.0070,0.9902,0.0006</t>
+  </si>
+  <si>
+    <t>0.0750,0.0426,0.8802,0.0037</t>
+  </si>
+  <si>
+    <t>0.0050,0.0105,0.9877,0.0031</t>
+  </si>
+  <si>
+    <t>0.1671,0.1307,0.7253,0.0446</t>
+  </si>
+  <si>
+    <t>0.4300,0.1692,0.4374,0.0188</t>
+  </si>
+  <si>
+    <t>0.4183,0.0497,0.5464,0.0642</t>
+  </si>
+  <si>
+    <t>0.4682,0.0097,0.6908,0.0097</t>
+  </si>
+  <si>
+    <t>0.8254,0.0018,0.2975,0.0037</t>
+  </si>
+  <si>
+    <t>0.9924,0.0017,0.0001,0.0013</t>
+  </si>
+  <si>
+    <t>0.9936,0.0048,0.0002,0.0003</t>
+  </si>
+  <si>
+    <t>0.9928,0.0041,0.0003,0.0005</t>
+  </si>
+  <si>
+    <t>0.9889,0.0125,0.0013,0.0002</t>
+  </si>
+  <si>
+    <t>0.9849,0.0075,0.0003,0.0014</t>
+  </si>
+  <si>
+    <t>0.9943,0.0060,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9812,0.0352,0.0012,0.0001</t>
+  </si>
+  <si>
+    <t>0.9841,0.0158,0.0007,0.0008</t>
+  </si>
+  <si>
+    <t>0.0231,0.0364,0.9563,0.0008</t>
+  </si>
+  <si>
+    <t>0.0028,0.3468,0.9776,0.0020</t>
+  </si>
+  <si>
+    <t>0.0147,0.0126,0.9785,0.0026</t>
+  </si>
+  <si>
+    <t>0.1509,0.0237,0.8360,0.0005</t>
+  </si>
+  <si>
+    <t>0.0141,0.0234,0.9690,0.0055</t>
+  </si>
+  <si>
+    <t>0.3826,0.0238,0.4746,0.1237</t>
+  </si>
+  <si>
+    <t>0.3964,0.0361,0.6481,0.0268</t>
+  </si>
+  <si>
+    <t>0.0340,0.0403,0.9201,0.0289</t>
+  </si>
+  <si>
+    <t>0.6848,0.0010,0.0004,0.5756</t>
+  </si>
+  <si>
+    <t>0.0175,0.1097,0.0080,0.9763</t>
+  </si>
+  <si>
+    <t>0.0752,0.0016,0.0029,0.9729</t>
+  </si>
+  <si>
+    <t>0.0062,0.0002,0.0025,0.9957</t>
+  </si>
+  <si>
+    <t>0.0010,0.0046,0.0038,0.9979</t>
+  </si>
+  <si>
+    <t>0.3384,0.1393,0.0266,0.6464</t>
   </si>
 </sst>
 </file>
@@ -1959,7 +1968,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1973,7 +1982,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1984,10 +1993,10 @@
         <v>259</v>
       </c>
       <c r="C4" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D4" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -2001,7 +2010,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2015,7 +2024,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2029,7 +2038,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2043,7 +2052,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2057,7 +2066,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2071,7 +2080,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2085,7 +2094,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2099,7 +2108,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2113,7 +2122,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2124,10 +2133,10 @@
         <v>259</v>
       </c>
       <c r="C14" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D14" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2138,10 +2147,10 @@
         <v>261</v>
       </c>
       <c r="C15" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2155,7 +2164,7 @@
         <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2169,7 +2178,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2183,7 +2192,7 @@
         <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2197,7 +2206,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2211,7 +2220,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2225,7 +2234,7 @@
         <v>259</v>
       </c>
       <c r="D21" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2236,10 +2245,10 @@
         <v>262</v>
       </c>
       <c r="C22" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="D22" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2253,7 +2262,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2264,10 +2273,10 @@
         <v>259</v>
       </c>
       <c r="C24" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D24" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2281,7 +2290,7 @@
         <v>261</v>
       </c>
       <c r="D25" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2295,7 +2304,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2309,7 +2318,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2323,7 +2332,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2337,7 +2346,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2351,7 +2360,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2362,10 +2371,10 @@
         <v>259</v>
       </c>
       <c r="C31" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="D31" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2379,7 +2388,7 @@
         <v>259</v>
       </c>
       <c r="D32" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2393,7 +2402,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2407,7 +2416,7 @@
         <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2421,7 +2430,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2432,10 +2441,10 @@
         <v>259</v>
       </c>
       <c r="C36" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D36" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2446,10 +2455,10 @@
         <v>259</v>
       </c>
       <c r="C37" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D37" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2463,7 +2472,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2477,7 +2486,7 @@
         <v>262</v>
       </c>
       <c r="D39" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2491,7 +2500,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2505,7 +2514,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2516,10 +2525,10 @@
         <v>261</v>
       </c>
       <c r="C42" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2533,7 +2542,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2547,7 +2556,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2561,7 +2570,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2572,10 +2581,10 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D46" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2589,7 +2598,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2603,7 +2612,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2617,7 +2626,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2631,7 +2640,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2645,7 +2654,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2659,7 +2668,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2673,7 +2682,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2687,7 +2696,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2701,7 +2710,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2715,7 +2724,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2729,7 +2738,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2743,7 +2752,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2757,7 +2766,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2771,7 +2780,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2785,7 +2794,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2799,7 +2808,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2810,10 +2819,10 @@
         <v>262</v>
       </c>
       <c r="C63" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D63" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2827,7 +2836,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2841,7 +2850,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2852,10 +2861,10 @@
         <v>263</v>
       </c>
       <c r="C66" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2869,7 +2878,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2883,7 +2892,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2897,7 +2906,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2911,7 +2920,7 @@
         <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2925,7 +2934,7 @@
         <v>259</v>
       </c>
       <c r="D71" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2939,7 +2948,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2953,7 +2962,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2967,7 +2976,7 @@
         <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2981,7 +2990,7 @@
         <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2995,7 +3004,7 @@
         <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3009,7 +3018,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3023,7 +3032,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3037,7 +3046,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3051,7 +3060,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3065,7 +3074,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3079,7 +3088,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3093,7 +3102,7 @@
         <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3107,7 +3116,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3121,7 +3130,7 @@
         <v>263</v>
       </c>
       <c r="D85" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3135,7 +3144,7 @@
         <v>261</v>
       </c>
       <c r="D86" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3149,7 +3158,7 @@
         <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3163,7 +3172,7 @@
         <v>263</v>
       </c>
       <c r="D88" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3177,7 +3186,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3191,7 +3200,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3205,7 +3214,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3219,7 +3228,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3233,7 +3242,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3247,7 +3256,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3261,7 +3270,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3275,7 +3284,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3289,7 +3298,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3303,7 +3312,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3317,7 +3326,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3331,7 +3340,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3345,7 +3354,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3359,7 +3368,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3373,7 +3382,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3387,7 +3396,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3401,7 +3410,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3415,7 +3424,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3429,7 +3438,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3443,7 +3452,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3457,7 +3466,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3471,7 +3480,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3485,7 +3494,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3499,7 +3508,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3513,7 +3522,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3527,7 +3536,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3538,10 +3547,10 @@
         <v>262</v>
       </c>
       <c r="C115" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D115" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3555,7 +3564,7 @@
         <v>259</v>
       </c>
       <c r="D116" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3569,7 +3578,7 @@
         <v>261</v>
       </c>
       <c r="D117" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3580,10 +3589,10 @@
         <v>259</v>
       </c>
       <c r="C118" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D118" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3594,10 +3603,10 @@
         <v>261</v>
       </c>
       <c r="C119" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D119" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3608,10 +3617,10 @@
         <v>262</v>
       </c>
       <c r="C120" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="D120" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3625,7 +3634,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3639,7 +3648,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3653,7 +3662,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3667,7 +3676,7 @@
         <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3681,7 +3690,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3695,7 +3704,7 @@
         <v>259</v>
       </c>
       <c r="D126" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3709,7 +3718,7 @@
         <v>262</v>
       </c>
       <c r="D127" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3723,7 +3732,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3737,7 +3746,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3751,7 +3760,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3765,7 +3774,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3779,7 +3788,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3793,7 +3802,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3807,7 +3816,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3821,7 +3830,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3835,7 +3844,7 @@
         <v>263</v>
       </c>
       <c r="D136" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3849,7 +3858,7 @@
         <v>263</v>
       </c>
       <c r="D137" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3860,10 +3869,10 @@
         <v>261</v>
       </c>
       <c r="C138" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D138" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3877,7 +3886,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3891,7 +3900,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3905,7 +3914,7 @@
         <v>259</v>
       </c>
       <c r="D141" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3919,7 +3928,7 @@
         <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3933,7 +3942,7 @@
         <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3947,7 +3956,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3961,7 +3970,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3975,7 +3984,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3989,7 +3998,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -4000,10 +4009,10 @@
         <v>263</v>
       </c>
       <c r="C148" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D148" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4017,7 +4026,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4028,10 +4037,10 @@
         <v>262</v>
       </c>
       <c r="C150" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4045,7 +4054,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4059,7 +4068,7 @@
         <v>259</v>
       </c>
       <c r="D152" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4073,7 +4082,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4084,10 +4093,10 @@
         <v>259</v>
       </c>
       <c r="C154" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="D154" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4101,7 +4110,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4115,7 +4124,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4126,10 +4135,10 @@
         <v>259</v>
       </c>
       <c r="C157" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4140,10 +4149,10 @@
         <v>259</v>
       </c>
       <c r="C158" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4157,7 +4166,7 @@
         <v>259</v>
       </c>
       <c r="D159" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4171,7 +4180,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4185,7 +4194,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4199,7 +4208,7 @@
         <v>262</v>
       </c>
       <c r="D162" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4213,7 +4222,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4227,7 +4236,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4241,7 +4250,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4255,7 +4264,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4269,7 +4278,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4283,7 +4292,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4297,7 +4306,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4311,7 +4320,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4325,7 +4334,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4339,7 +4348,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4350,10 +4359,10 @@
         <v>259</v>
       </c>
       <c r="C173" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D173" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4364,10 +4373,10 @@
         <v>259</v>
       </c>
       <c r="C174" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="D174" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4381,7 +4390,7 @@
         <v>259</v>
       </c>
       <c r="D175" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4392,10 +4401,10 @@
         <v>261</v>
       </c>
       <c r="C176" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D176" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4409,7 +4418,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4423,7 +4432,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4437,7 +4446,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4451,7 +4460,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4465,7 +4474,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4479,7 +4488,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4493,7 +4502,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4507,7 +4516,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4521,7 +4530,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4532,10 +4541,10 @@
         <v>261</v>
       </c>
       <c r="C186" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4549,7 +4558,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4563,7 +4572,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4577,7 +4586,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4588,10 +4597,10 @@
         <v>259</v>
       </c>
       <c r="C190" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4605,7 +4614,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4616,10 +4625,10 @@
         <v>259</v>
       </c>
       <c r="C192" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D192" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4633,7 +4642,7 @@
         <v>261</v>
       </c>
       <c r="D193" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4647,7 +4656,7 @@
         <v>262</v>
       </c>
       <c r="D194" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4658,10 +4667,10 @@
         <v>261</v>
       </c>
       <c r="C195" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D195" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4672,10 +4681,10 @@
         <v>259</v>
       </c>
       <c r="C196" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D196" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4689,7 +4698,7 @@
         <v>261</v>
       </c>
       <c r="D197" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4703,7 +4712,7 @@
         <v>259</v>
       </c>
       <c r="D198" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4717,7 +4726,7 @@
         <v>259</v>
       </c>
       <c r="D199" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4731,7 +4740,7 @@
         <v>259</v>
       </c>
       <c r="D200" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4745,7 +4754,7 @@
         <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4756,10 +4765,10 @@
         <v>259</v>
       </c>
       <c r="C202" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D202" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4770,10 +4779,10 @@
         <v>259</v>
       </c>
       <c r="C203" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4787,7 +4796,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4798,10 +4807,10 @@
         <v>259</v>
       </c>
       <c r="C205" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="D205" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4815,7 +4824,7 @@
         <v>259</v>
       </c>
       <c r="D206" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4829,7 +4838,7 @@
         <v>259</v>
       </c>
       <c r="D207" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4843,7 +4852,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4857,7 +4866,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4868,10 +4877,10 @@
         <v>261</v>
       </c>
       <c r="C210" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4885,7 +4894,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4899,7 +4908,7 @@
         <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4913,7 +4922,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4927,7 +4936,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4941,7 +4950,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4955,7 +4964,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4969,7 +4978,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4983,7 +4992,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4997,7 +5006,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5011,7 +5020,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5025,7 +5034,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5036,10 +5045,10 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D222" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5053,7 +5062,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5067,7 +5076,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5081,7 +5090,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5095,7 +5104,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5109,7 +5118,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5123,7 +5132,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5137,7 +5146,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5151,7 +5160,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5162,10 +5171,10 @@
         <v>261</v>
       </c>
       <c r="C231" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="D231" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5179,7 +5188,7 @@
         <v>261</v>
       </c>
       <c r="D232" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5190,10 +5199,10 @@
         <v>259</v>
       </c>
       <c r="C233" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D233" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5207,7 +5216,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5221,7 +5230,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5235,7 +5244,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5249,7 +5258,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5263,7 +5272,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5277,7 +5286,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5291,7 +5300,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5305,7 +5314,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5319,7 +5328,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5333,7 +5342,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5347,7 +5356,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5361,7 +5370,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5375,7 +5384,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5389,7 +5398,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5400,10 +5409,10 @@
         <v>261</v>
       </c>
       <c r="C248" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D248" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5417,7 +5426,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5431,7 +5440,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5442,10 +5451,10 @@
         <v>259</v>
       </c>
       <c r="C251" t="s">
-        <v>260</v>
+        <v>267</v>
       </c>
       <c r="D251" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5459,7 +5468,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5473,7 +5482,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5487,7 +5496,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5501,7 +5510,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5512,10 +5521,10 @@
         <v>259</v>
       </c>
       <c r="C256" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D256" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
     </row>
   </sheetData>
